--- a/data/맨홀이력.xlsx
+++ b/data/맨홀이력.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="33">
   <si>
     <t>구간</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -166,6 +166,9 @@
   <si>
     <t>보수횟수</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접속제 침수(수위추정)</t>
   </si>
 </sst>
 </file>
@@ -1598,11 +1601,20 @@
       <c r="AF17" s="4">
         <v>1600</v>
       </c>
+      <c r="AH17" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ17" s="4">
         <v>1200</v>
       </c>
+      <c r="AL17" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN17" s="4">
         <v>1600</v>
+      </c>
+      <c r="AP17" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ17" s="1">
         <f t="shared" si="0"/>
@@ -1805,11 +1817,17 @@
       <c r="AF21" s="4">
         <v>1000</v>
       </c>
+      <c r="AH21" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ21" s="4">
         <v>500</v>
       </c>
       <c r="AN21" s="4">
         <v>1000</v>
+      </c>
+      <c r="AP21" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="AQ21" s="1">
         <f t="shared" si="0"/>
@@ -1910,11 +1928,20 @@
       <c r="AF23" s="4">
         <v>1400</v>
       </c>
+      <c r="AH23" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ23" s="4">
         <v>1400</v>
       </c>
+      <c r="AL23" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN23" s="4">
         <v>1400</v>
+      </c>
+      <c r="AP23" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ23" s="1">
         <f t="shared" si="0"/>
@@ -2573,6 +2600,9 @@
       <c r="AF36" s="4">
         <v>900</v>
       </c>
+      <c r="AH36" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ36" s="4">
         <v>700</v>
       </c>
@@ -2581,6 +2611,9 @@
       </c>
       <c r="AN36" s="4">
         <v>900</v>
+      </c>
+      <c r="AP36" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ36" s="1">
         <f t="shared" si="0"/>
@@ -4253,11 +4286,20 @@
       <c r="AF3" s="4">
         <v>600</v>
       </c>
+      <c r="AH3" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ3" s="4">
         <v>600</v>
       </c>
+      <c r="AL3" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN3" s="4">
         <v>600</v>
+      </c>
+      <c r="AP3" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ3" s="1">
         <f>COUNTA(D3,G3,J3,M3,P3,W3,AA3,AE3,AI3,AM3)</f>
@@ -4310,11 +4352,20 @@
       <c r="AF4" s="4">
         <v>700</v>
       </c>
+      <c r="AH4" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ4" s="4">
         <v>800</v>
       </c>
+      <c r="AL4" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN4" s="4">
         <v>700</v>
+      </c>
+      <c r="AP4" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ4" s="1">
         <f t="shared" ref="AQ4:AQ45" si="0">COUNTA(D4,G4,J4,M4,P4,W4,AA4,AE4,AI4,AM4)</f>
@@ -4373,11 +4424,20 @@
       <c r="AF5" s="4">
         <v>700</v>
       </c>
+      <c r="AH5" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ5" s="4">
         <v>600</v>
+      </c>
+      <c r="AL5" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AN5" s="4">
         <v>700</v>
+      </c>
+      <c r="AP5" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ5" s="1">
         <f t="shared" si="0"/>
@@ -4433,11 +4493,20 @@
       <c r="AF6" s="4">
         <v>500</v>
       </c>
+      <c r="AH6" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ6" s="4">
         <v>700</v>
       </c>
+      <c r="AL6" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN6" s="4">
         <v>500</v>
+      </c>
+      <c r="AP6" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ6" s="1">
         <f t="shared" si="0"/>
@@ -4490,11 +4559,20 @@
       <c r="AF7" s="4">
         <v>600</v>
       </c>
+      <c r="AH7" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ7" s="4">
         <v>600</v>
       </c>
+      <c r="AL7" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN7" s="4">
         <v>600</v>
+      </c>
+      <c r="AP7" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ7" s="1">
         <f t="shared" si="0"/>
@@ -4547,11 +4625,20 @@
       <c r="AF8" s="4">
         <v>600</v>
       </c>
+      <c r="AH8" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ8" s="4">
         <v>500</v>
       </c>
+      <c r="AL8" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN8" s="4">
         <v>600</v>
+      </c>
+      <c r="AP8" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ8" s="1">
         <f t="shared" si="0"/>
@@ -4601,11 +4688,17 @@
       <c r="AF9" s="4">
         <v>600</v>
       </c>
+      <c r="AH9" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ9" s="4">
         <v>500</v>
       </c>
       <c r="AN9" s="4">
         <v>600</v>
+      </c>
+      <c r="AP9" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ9" s="1">
         <f t="shared" si="0"/>
@@ -4709,11 +4802,20 @@
       <c r="AF11" s="4">
         <v>700</v>
       </c>
+      <c r="AH11" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ11" s="4">
         <v>600</v>
+      </c>
+      <c r="AL11" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AN11" s="4">
         <v>700</v>
+      </c>
+      <c r="AP11" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ11" s="1">
         <f t="shared" si="0"/>
@@ -4763,11 +4865,17 @@
       <c r="AF12" s="4">
         <v>700</v>
       </c>
+      <c r="AH12" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ12" s="4">
         <v>500</v>
       </c>
       <c r="AN12" s="4">
         <v>700</v>
+      </c>
+      <c r="AP12" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ12" s="1">
         <f t="shared" si="0"/>
@@ -4961,11 +5069,20 @@
       <c r="AF16" s="4">
         <v>700</v>
       </c>
+      <c r="AH16" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ16" s="4">
         <v>400</v>
       </c>
+      <c r="AL16" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN16" s="4">
         <v>700</v>
+      </c>
+      <c r="AP16" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ16" s="1">
         <f t="shared" si="0"/>
@@ -5066,11 +5183,20 @@
       <c r="AF18" s="4">
         <v>1200</v>
       </c>
+      <c r="AH18" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ18" s="4">
         <v>1000</v>
       </c>
+      <c r="AL18" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN18" s="4">
         <v>1200</v>
+      </c>
+      <c r="AP18" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ18" s="1">
         <f t="shared" si="0"/>
@@ -5525,6 +5651,9 @@
       <c r="AJ26" s="4">
         <v>600</v>
       </c>
+      <c r="AL26" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN26" s="4">
         <v>500</v>
       </c>
@@ -5573,11 +5702,17 @@
       <c r="AF27" s="4">
         <v>700</v>
       </c>
+      <c r="AH27" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ27" s="4">
         <v>300</v>
       </c>
       <c r="AN27" s="4">
         <v>700</v>
+      </c>
+      <c r="AP27" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ27" s="1">
         <f t="shared" si="0"/>
@@ -5642,6 +5777,9 @@
       <c r="AJ28" s="4">
         <v>1100</v>
       </c>
+      <c r="AL28" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN28" s="4">
         <v>500</v>
       </c>
@@ -5696,12 +5834,21 @@
       <c r="AF29" s="4">
         <v>700</v>
       </c>
+      <c r="AH29" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ29" s="4">
         <v>600</v>
+      </c>
+      <c r="AL29" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AN29" s="4">
         <v>700</v>
       </c>
+      <c r="AP29" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AQ29" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5761,6 +5908,9 @@
       </c>
       <c r="AJ30" s="4">
         <v>1300</v>
+      </c>
+      <c r="AL30" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AN30" s="4">
         <v>1200</v>
@@ -5819,11 +5969,20 @@
       <c r="AF31" s="4">
         <v>1200</v>
       </c>
+      <c r="AH31" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ31" s="4">
         <v>1100</v>
       </c>
+      <c r="AL31" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN31" s="4">
         <v>1200</v>
+      </c>
+      <c r="AP31" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ31" s="1">
         <f t="shared" si="0"/>
@@ -5948,6 +6107,9 @@
       <c r="AJ33" s="4">
         <v>1200</v>
       </c>
+      <c r="AL33" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN33" s="4">
         <v>900</v>
       </c>
@@ -6002,11 +6164,20 @@
       <c r="AF34" s="4">
         <v>1000</v>
       </c>
+      <c r="AH34" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ34" s="4">
         <v>900</v>
       </c>
+      <c r="AL34" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN34" s="4">
         <v>1000</v>
+      </c>
+      <c r="AP34" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ34" s="1">
         <f t="shared" si="0"/>
@@ -6122,11 +6293,20 @@
       <c r="AF36" s="4">
         <v>2000</v>
       </c>
+      <c r="AH36" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ36" s="4">
         <v>1800</v>
       </c>
+      <c r="AL36" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN36" s="4">
         <v>2000</v>
+      </c>
+      <c r="AP36" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ36" s="1">
         <f t="shared" si="0"/>
@@ -6188,6 +6368,9 @@
       <c r="AJ37" s="4">
         <v>1300</v>
       </c>
+      <c r="AL37" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN37" s="4">
         <v>1100</v>
       </c>
@@ -6245,14 +6428,23 @@
       <c r="AF38" s="4">
         <v>1000</v>
       </c>
+      <c r="AH38" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AI38" s="9" t="s">
         <v>21</v>
       </c>
       <c r="AJ38" s="4">
         <v>1000</v>
       </c>
+      <c r="AL38" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN38" s="4">
         <v>1000</v>
+      </c>
+      <c r="AP38" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ38" s="1">
         <f t="shared" si="0"/>
@@ -6308,14 +6500,23 @@
       <c r="AF39" s="4">
         <v>1000</v>
       </c>
+      <c r="AH39" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AI39" s="9" t="s">
         <v>21</v>
       </c>
       <c r="AJ39" s="4">
         <v>1100</v>
       </c>
+      <c r="AL39" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN39" s="4">
         <v>1000</v>
+      </c>
+      <c r="AP39" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ39" s="1">
         <f t="shared" si="0"/>
@@ -6374,6 +6575,9 @@
       <c r="AJ40" s="4">
         <v>1400</v>
       </c>
+      <c r="AL40" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN40" s="4">
         <v>1200</v>
       </c>
@@ -6428,11 +6632,20 @@
       <c r="AF41" s="4">
         <v>1400</v>
       </c>
+      <c r="AH41" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ41" s="4">
         <v>1500</v>
       </c>
+      <c r="AL41" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN41" s="4">
         <v>1400</v>
+      </c>
+      <c r="AP41" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ41" s="1">
         <f t="shared" si="0"/>

--- a/data/맨홀이력.xlsx
+++ b/data/맨홀이력.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="35">
   <si>
     <t>구간</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -169,6 +169,12 @@
   </si>
   <si>
     <t>접속제 침수(수위추정)</t>
+  </si>
+  <si>
+    <t>관로구방수장치 보수필요 / 접속제 침수(수위추정)</t>
+  </si>
+  <si>
+    <t>부분보수필요 / 접속제 침수(수위추정)</t>
   </si>
 </sst>
 </file>
@@ -987,7 +993,7 @@
         <v>24</v>
       </c>
       <c r="AD5" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AE5" s="9" t="s">
         <v>21</v>
@@ -997,6 +1003,9 @@
       </c>
       <c r="AJ5" s="4">
         <v>1400</v>
+      </c>
+      <c r="AL5" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AN5" s="4">
         <v>900</v>
@@ -1499,6 +1508,9 @@
       <c r="AJ15" s="4">
         <v>2200</v>
       </c>
+      <c r="AL15" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN15" s="4">
         <v>1800</v>
       </c>
@@ -1650,7 +1662,7 @@
         <v>24</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="X18" s="4">
         <v>1200</v>
@@ -1659,7 +1671,7 @@
         <v>24</v>
       </c>
       <c r="Z18" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AB18" s="4">
         <v>1000</v>
@@ -1914,7 +1926,7 @@
         <v>24</v>
       </c>
       <c r="Z23" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AB23" s="4">
         <v>1500</v>
@@ -3306,7 +3318,7 @@
         <v>24</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="X50" s="10">
         <v>2000</v>
@@ -3482,11 +3494,17 @@
       <c r="AF53" s="4">
         <v>1200</v>
       </c>
+      <c r="AH53" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ53" s="4">
         <v>900</v>
       </c>
       <c r="AN53" s="4">
         <v>1200</v>
+      </c>
+      <c r="AP53" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ53" s="1">
         <f t="shared" si="0"/>
@@ -3522,7 +3540,7 @@
         <v>24</v>
       </c>
       <c r="V54" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="X54" s="10">
         <v>700</v>
@@ -3531,7 +3549,7 @@
         <v>24</v>
       </c>
       <c r="Z54" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AC54" s="4" t="s">
         <v>25</v>
@@ -3539,11 +3557,20 @@
       <c r="AF54" s="4">
         <v>1000</v>
       </c>
+      <c r="AH54" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ54" s="4">
         <v>800</v>
       </c>
+      <c r="AL54" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN54" s="4">
         <v>1000</v>
+      </c>
+      <c r="AP54" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ54" s="1">
         <f t="shared" si="0"/>
@@ -4742,11 +4769,17 @@
       <c r="AF10" s="4">
         <v>500</v>
       </c>
+      <c r="AH10" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ10" s="4">
         <v>200</v>
       </c>
       <c r="AN10" s="4">
         <v>500</v>
+      </c>
+      <c r="AP10" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="AQ10" s="1">
         <f t="shared" si="0"/>
@@ -4955,12 +4988,18 @@
       <c r="U14" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="V14" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="X14" s="4">
         <v>300</v>
       </c>
       <c r="Y14" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="Z14" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AB14" s="4">
         <v>100</v>
       </c>
@@ -4970,11 +5009,20 @@
       <c r="AF14" s="4">
         <v>700</v>
       </c>
+      <c r="AH14" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ14" s="4">
         <v>400</v>
       </c>
+      <c r="AL14" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AN14" s="4">
         <v>700</v>
+      </c>
+      <c r="AP14" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="AQ14" s="1">
         <f t="shared" si="0"/>
@@ -5003,11 +5051,17 @@
       <c r="U15" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="V15" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="X15" s="4">
         <v>600</v>
       </c>
       <c r="Y15" s="4" t="s">
         <v>25</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="AB15" s="4">
         <v>500</v>
@@ -5015,14 +5069,26 @@
       <c r="AC15" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="AD15" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AF15" s="4">
         <v>600</v>
       </c>
+      <c r="AH15" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ15" s="4">
         <v>600</v>
       </c>
+      <c r="AL15" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AN15" s="4">
         <v>600</v>
+      </c>
+      <c r="AP15" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="AQ15" s="1">
         <f t="shared" si="0"/>
@@ -5060,11 +5126,17 @@
       <c r="Y16" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="Z16" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AB16" s="4">
         <v>300</v>
       </c>
       <c r="AC16" s="4" t="s">
         <v>25</v>
+      </c>
+      <c r="AD16" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AF16" s="4">
         <v>700</v>
@@ -5111,11 +5183,17 @@
       <c r="U17" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="V17" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="X17" s="4">
         <v>600</v>
       </c>
       <c r="Y17" s="4" t="s">
         <v>25</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="AB17" s="4">
         <v>500</v>
@@ -5126,11 +5204,20 @@
       <c r="AF17" s="4">
         <v>600</v>
       </c>
+      <c r="AH17" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ17" s="4">
         <v>600</v>
       </c>
+      <c r="AL17" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AN17" s="4">
         <v>600</v>
+      </c>
+      <c r="AP17" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="AQ17" s="1">
         <f t="shared" si="0"/>
@@ -5225,26 +5312,44 @@
       <c r="U19" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="V19" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="X19" s="4">
         <v>300</v>
       </c>
       <c r="Y19" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="Z19" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AB19" s="4">
         <v>500</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="AD19" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AF19" s="4">
         <v>600</v>
+      </c>
+      <c r="AH19" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="AJ19" s="4">
         <v>500</v>
       </c>
+      <c r="AL19" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AN19" s="4">
         <v>600</v>
+      </c>
+      <c r="AP19" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="AQ19" s="1">
         <f t="shared" si="0"/>
@@ -5274,7 +5379,7 @@
         <v>24</v>
       </c>
       <c r="V20" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="X20" s="4">
         <v>100</v>
@@ -5283,7 +5388,7 @@
         <v>24</v>
       </c>
       <c r="Z20" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AB20" s="4">
         <v>0</v>
@@ -5297,11 +5402,20 @@
       <c r="AF20" s="4">
         <v>200</v>
       </c>
+      <c r="AH20" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ20" s="4">
         <v>100</v>
       </c>
+      <c r="AL20" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN20" s="4">
         <v>200</v>
+      </c>
+      <c r="AP20" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ20" s="1">
         <f t="shared" si="0"/>
@@ -5346,7 +5460,7 @@
         <v>24</v>
       </c>
       <c r="Z21" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AB21" s="4">
         <v>400</v>
@@ -5360,11 +5474,20 @@
       <c r="AF21" s="4">
         <v>1200</v>
       </c>
+      <c r="AH21" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ21" s="4">
         <v>900</v>
       </c>
+      <c r="AL21" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN21" s="4">
         <v>1200</v>
+      </c>
+      <c r="AP21" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ21" s="1">
         <f t="shared" si="0"/>
@@ -5534,6 +5657,9 @@
       <c r="AJ24" s="4">
         <v>900</v>
       </c>
+      <c r="AL24" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN24" s="4">
         <v>700</v>
       </c>
@@ -5594,6 +5720,9 @@
       <c r="AJ25" s="4">
         <v>900</v>
       </c>
+      <c r="AL25" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN25" s="4">
         <v>800</v>
       </c>
@@ -6044,6 +6173,9 @@
       <c r="AJ32" s="4">
         <v>700</v>
       </c>
+      <c r="AL32" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN32" s="4">
         <v>500</v>
       </c>
@@ -6207,7 +6339,7 @@
         <v>24</v>
       </c>
       <c r="V35" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="X35" s="4">
         <v>700</v>
@@ -6216,7 +6348,7 @@
         <v>24</v>
       </c>
       <c r="Z35" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AB35" s="4">
         <v>600</v>
@@ -6225,16 +6357,25 @@
         <v>24</v>
       </c>
       <c r="AD35" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AF35" s="4">
         <v>800</v>
       </c>
+      <c r="AH35" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ35" s="4">
         <v>700</v>
       </c>
+      <c r="AL35" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN35" s="4">
         <v>800</v>
+      </c>
+      <c r="AP35" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ35" s="1">
         <f t="shared" si="0"/>
@@ -6710,6 +6851,9 @@
       <c r="AJ42" s="4">
         <v>1500</v>
       </c>
+      <c r="AL42" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN42" s="4">
         <v>1000</v>
       </c>
@@ -6744,7 +6888,7 @@
         <v>24</v>
       </c>
       <c r="V43" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="X43" s="4">
         <v>400</v>
@@ -6753,7 +6897,7 @@
         <v>24</v>
       </c>
       <c r="Z43" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AB43" s="4">
         <v>700</v>
@@ -6762,7 +6906,7 @@
         <v>24</v>
       </c>
       <c r="AD43" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AE43" s="9" t="s">
         <v>21</v>
@@ -6770,11 +6914,20 @@
       <c r="AF43" s="4">
         <v>600</v>
       </c>
+      <c r="AH43" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ43" s="4">
         <v>600</v>
       </c>
+      <c r="AL43" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="AN43" s="4">
         <v>600</v>
+      </c>
+      <c r="AP43" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="AQ43" s="1">
         <f t="shared" si="0"/>
